--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:10:03+00:00</t>
+    <t>2023-03-24T14:10:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:10:14+00:00</t>
+    <t>2023-03-24T14:14:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:14:45+00:00</t>
+    <t>2023-03-24T14:36:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:36:11+00:00</t>
+    <t>2023-03-24T14:36:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:36:59+00:00</t>
+    <t>2023-03-24T14:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T14:42:38+00:00</t>
+    <t>2023-03-24T15:33:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:33:20+00:00</t>
+    <t>2023-03-24T15:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:33:53+00:00</t>
+    <t>2023-03-24T15:38:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-24T15:38:14+00:00</t>
+    <t>2023-03-26T08:37:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T08:37:00+00:00</t>
+    <t>2023-03-26T08:42:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2700" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2700" uniqueCount="589">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T08:42:47+00:00</t>
+    <t>2023-03-26T09:01:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -836,6 +836,9 @@
   </si>
   <si>
     <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>HIV lab service request identifier</t>
   </si>
   <si>
     <t>CodeableConcept.text</t>
@@ -5285,7 +5288,7 @@
         <v>81</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>81</v>
+        <v>267</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>81</v>
@@ -5324,7 +5327,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5342,10 +5345,10 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -5356,10 +5359,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5385,29 +5388,29 @@
         <v>103</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>81</v>
@@ -5443,7 +5446,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5461,10 +5464,10 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5475,10 +5478,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5504,13 +5507,13 @@
         <v>163</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5524,7 +5527,7 @@
         <v>81</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>81</v>
@@ -5560,7 +5563,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5578,10 +5581,10 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -5592,10 +5595,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5618,13 +5621,13 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5675,7 +5678,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5693,10 +5696,10 @@
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5707,10 +5710,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5733,16 +5736,16 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5792,7 +5795,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5810,10 +5813,10 @@
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5824,10 +5827,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5850,16 +5853,16 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5909,7 +5912,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5924,13 +5927,13 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
@@ -5941,10 +5944,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5970,13 +5973,13 @@
         <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6026,7 +6029,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6041,13 +6044,13 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -6058,14 +6061,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6084,13 +6087,13 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6141,7 +6144,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6156,13 +6159,13 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -6173,14 +6176,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6199,13 +6202,13 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6256,7 +6259,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6271,13 +6274,13 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -6288,14 +6291,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6317,16 +6320,16 @@
         <v>147</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6375,7 +6378,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6390,13 +6393,13 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6407,10 +6410,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6436,13 +6439,13 @@
         <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6471,10 +6474,10 @@
         <v>181</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6492,7 +6495,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>89</v>
@@ -6507,27 +6510,27 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6553,13 +6556,13 @@
         <v>109</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6570,7 +6573,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -6588,10 +6591,10 @@
         <v>181</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6609,7 +6612,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>89</v>
@@ -6624,16 +6627,16 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>132</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6641,10 +6644,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6670,16 +6673,16 @@
         <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6704,13 +6707,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6728,7 +6731,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6746,13 +6749,13 @@
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -6760,10 +6763,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6789,10 +6792,10 @@
         <v>109</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6800,7 +6803,7 @@
         <v>81</v>
       </c>
       <c r="Q40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="R40" t="s" s="2">
         <v>81</v>
@@ -6824,10 +6827,10 @@
         <v>181</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
@@ -6845,7 +6848,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6860,16 +6863,16 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
@@ -6877,10 +6880,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6906,67 +6909,67 @@
         <v>253</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q41" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="R41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="P41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q41" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="R41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6981,13 +6984,13 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -6998,14 +7001,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7027,13 +7030,13 @@
         <v>188</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7063,7 +7066,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -7081,7 +7084,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7096,27 +7099,27 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7228,10 +7231,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7345,10 +7348,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7464,10 +7467,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7512,7 +7515,7 @@
         <v>81</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>81</v>
@@ -7551,7 +7554,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7569,10 +7572,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7583,14 +7586,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7612,13 +7615,13 @@
         <v>188</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7644,13 +7647,13 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
@@ -7668,7 +7671,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7677,7 +7680,7 @@
         <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>101</v>
@@ -7686,24 +7689,24 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7726,17 +7729,17 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7785,7 +7788,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7803,10 +7806,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7817,10 +7820,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7843,13 +7846,13 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7900,7 +7903,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -7915,31 +7918,31 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7958,13 +7961,13 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8015,7 +8018,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8030,31 +8033,31 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8073,13 +8076,13 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8118,17 +8121,17 @@
         <v>81</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8143,33 +8146,33 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8188,13 +8191,13 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8245,7 +8248,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8260,27 +8263,27 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8303,13 +8306,13 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8336,13 +8339,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8360,7 +8363,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8381,25 +8384,25 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8418,13 +8421,13 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8475,7 +8478,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8490,31 +8493,31 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8533,16 +8536,16 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8592,7 +8595,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8607,31 +8610,31 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8653,13 +8656,13 @@
         <v>188</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8685,13 +8688,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8709,7 +8712,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8724,16 +8727,16 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8741,14 +8744,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8767,16 +8770,16 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8826,7 +8829,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8841,16 +8844,16 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8858,10 +8861,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8887,10 +8890,10 @@
         <v>188</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8917,13 +8920,13 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
@@ -8941,7 +8944,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8962,10 +8965,10 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -8973,10 +8976,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8999,13 +9002,13 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9056,7 +9059,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9077,10 +9080,10 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9088,10 +9091,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9117,13 +9120,13 @@
         <v>188</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9153,7 +9156,7 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9171,7 +9174,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9186,16 +9189,16 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
@@ -9203,10 +9206,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9318,10 +9321,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9435,10 +9438,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9554,10 +9557,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9602,7 +9605,7 @@
         <v>81</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>81</v>
@@ -9641,7 +9644,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9659,10 +9662,10 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -9673,10 +9676,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9699,16 +9702,16 @@
         <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9758,7 +9761,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9773,16 +9776,16 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
@@ -9790,10 +9793,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9816,13 +9819,13 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9873,7 +9876,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9888,13 +9891,13 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -9905,14 +9908,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9931,16 +9934,16 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9990,7 +9993,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10005,13 +10008,13 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -10022,10 +10025,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10048,16 +10051,16 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10107,7 +10110,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10125,10 +10128,10 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -10139,14 +10142,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10168,16 +10171,16 @@
         <v>188</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -10202,13 +10205,13 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -10226,7 +10229,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10244,24 +10247,24 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10284,13 +10287,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10341,7 +10344,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10356,27 +10359,27 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10402,10 +10405,10 @@
         <v>163</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10456,7 +10459,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10474,10 +10477,10 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -10488,10 +10491,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10514,16 +10517,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10573,7 +10576,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10588,13 +10591,13 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>132</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:01:05+00:00</t>
+    <t>2023-03-26T09:02:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:02:01+00:00</t>
+    <t>2023-03-26T09:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T09:07:12+00:00</t>
+    <t>2023-03-26T10:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:35:39+00:00</t>
+    <t>2023-03-26T10:35:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:35:51+00:00</t>
+    <t>2023-03-26T10:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T10:42:59+00:00</t>
+    <t>2023-03-26T11:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:08:41+00:00</t>
+    <t>2023-03-26T11:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:16:53+00:00</t>
+    <t>2023-03-26T11:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:17:47+00:00</t>
+    <t>2023-03-26T11:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-26T11:23:31+00:00</t>
+    <t>2023-03-27T11:26:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -10275,7 +10275,7 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>81</v>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T11:26:57+00:00</t>
+    <t>2023-03-27T11:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T11:35:12+00:00</t>
+    <t>2023-03-27T12:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:01:10+00:00</t>
+    <t>2023-03-27T12:02:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:02:15+00:00</t>
+    <t>2023-03-27T12:10:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-27T12:10:50+00:00</t>
+    <t>2023-03-28T07:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8758,7 +8758,7 @@
         <v>89</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:37:59+00:00</t>
+    <t>2023-03-28T07:45:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:45:58+00:00</t>
+    <t>2023-03-28T07:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-28T07:53:05+00:00</t>
+    <t>2023-03-29T10:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T10:46:03+00:00</t>
+    <t>2023-03-29T10:52:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T10:52:43+00:00</t>
+    <t>2023-03-29T11:10:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-29T11:10:06+00:00</t>
+    <t>2023-03-31T13:54:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T13:54:07+00:00</t>
+    <t>2023-03-31T13:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-31T13:55:03+00:00</t>
+    <t>2023-04-01T08:28:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:28:06+00:00</t>
+    <t>2023-04-01T08:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:29:12+00:00</t>
+    <t>2023-04-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:49:37+00:00</t>
+    <t>2023-04-01T08:50:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-01T08:50:39+00:00</t>
+    <t>2023-04-03T05:56:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$72</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T05:56:04+00:00</t>
+    <t>2023-04-03T09:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1966,6 +1969,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2309,7 +2327,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2424,7 +2442,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>88</v>
       </c>
@@ -2541,7 +2559,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>96</v>
       </c>
@@ -2656,7 +2674,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>102</v>
       </c>
@@ -2773,7 +2791,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>108</v>
       </c>
@@ -2890,7 +2908,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>117</v>
       </c>
@@ -3007,7 +3025,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>125</v>
       </c>
@@ -3124,7 +3142,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>133</v>
       </c>
@@ -3241,7 +3259,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>141</v>
       </c>
@@ -3360,7 +3378,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>146</v>
       </c>
@@ -3477,7 +3495,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>159</v>
       </c>
@@ -3596,7 +3614,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>161</v>
       </c>
@@ -3711,7 +3729,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>168</v>
       </c>
@@ -3828,7 +3846,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>175</v>
       </c>
@@ -3947,7 +3965,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>186</v>
       </c>
@@ -4066,7 +4084,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>198</v>
       </c>
@@ -4181,7 +4199,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>200</v>
       </c>
@@ -4298,7 +4316,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>202</v>
       </c>
@@ -4417,7 +4435,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>212</v>
       </c>
@@ -4532,7 +4550,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>214</v>
       </c>
@@ -4649,7 +4667,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>216</v>
       </c>
@@ -4768,7 +4786,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>226</v>
       </c>
@@ -4885,7 +4903,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>234</v>
       </c>
@@ -5002,7 +5020,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>242</v>
       </c>
@@ -5119,7 +5137,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>251</v>
       </c>
@@ -5238,7 +5256,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>261</v>
       </c>
@@ -5357,7 +5375,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>271</v>
       </c>
@@ -5476,7 +5494,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>282</v>
       </c>
@@ -5593,7 +5611,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>291</v>
       </c>
@@ -5708,7 +5726,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>299</v>
       </c>
@@ -5825,7 +5843,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>308</v>
       </c>
@@ -5942,7 +5960,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>316</v>
       </c>
@@ -6059,7 +6077,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>321</v>
       </c>
@@ -6174,7 +6192,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>329</v>
       </c>
@@ -6289,7 +6307,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>337</v>
       </c>
@@ -6408,7 +6426,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>346</v>
       </c>
@@ -6525,7 +6543,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>357</v>
       </c>
@@ -6642,7 +6660,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>367</v>
       </c>
@@ -6761,7 +6779,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>377</v>
       </c>
@@ -6878,7 +6896,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>387</v>
       </c>
@@ -6999,7 +7017,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>395</v>
       </c>
@@ -7114,7 +7132,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>406</v>
       </c>
@@ -7229,7 +7247,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>407</v>
       </c>
@@ -7346,7 +7364,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>408</v>
       </c>
@@ -7465,7 +7483,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>409</v>
       </c>
@@ -7584,7 +7602,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>411</v>
       </c>
@@ -7701,7 +7719,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>420</v>
       </c>
@@ -7818,7 +7836,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>426</v>
       </c>
@@ -7933,7 +7951,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>435</v>
       </c>
@@ -8048,7 +8066,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>445</v>
       </c>
@@ -8161,7 +8179,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>457</v>
       </c>
@@ -8278,7 +8296,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>459</v>
       </c>
@@ -8393,7 +8411,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>467</v>
       </c>
@@ -8508,7 +8526,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>476</v>
       </c>
@@ -8625,7 +8643,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>487</v>
       </c>
@@ -8742,7 +8760,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>498</v>
       </c>
@@ -8859,7 +8877,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>507</v>
       </c>
@@ -8974,7 +8992,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>513</v>
       </c>
@@ -9089,7 +9107,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>517</v>
       </c>
@@ -9204,7 +9222,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>526</v>
       </c>
@@ -9319,7 +9337,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>527</v>
       </c>
@@ -9436,7 +9454,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>528</v>
       </c>
@@ -9555,7 +9573,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>529</v>
       </c>
@@ -9674,7 +9692,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>531</v>
       </c>
@@ -9791,7 +9809,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>539</v>
       </c>
@@ -9906,7 +9924,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>546</v>
       </c>
@@ -10023,7 +10041,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>555</v>
       </c>
@@ -10036,13 +10054,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>81</v>
@@ -10140,7 +10158,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>562</v>
       </c>
@@ -10259,7 +10277,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>572</v>
       </c>
@@ -10374,7 +10392,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>578</v>
       </c>
@@ -10489,7 +10507,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>582</v>
       </c>
@@ -10607,6 +10625,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AO72">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI71">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:35:38+00:00</t>
+    <t>2023-04-03T09:37:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:37:11+00:00</t>
+    <t>2023-04-03T09:57:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T09:57:00+00:00</t>
+    <t>2023-04-03T10:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -10054,13 +10054,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>81</v>
@@ -10296,7 +10296,7 @@
         <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>81</v>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:19:29+00:00</t>
+    <t>2023-04-03T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:20:09+00:00</t>
+    <t>2023-04-03T10:41:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-03T10:41:47+00:00</t>
+    <t>2023-04-04T06:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T06:46:45+00:00</t>
+    <t>2023-04-04T06:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T06:47:21+00:00</t>
+    <t>2023-04-04T07:17:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T07:17:27+00:00</t>
+    <t>2023-04-04T08:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:23:07+00:00</t>
+    <t>2023-04-04T08:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T08:37:07+00:00</t>
+    <t>2023-04-04T09:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:08:50+00:00</t>
+    <t>2023-04-04T09:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:09:26+00:00</t>
+    <t>2023-04-04T09:19:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:19:23+00:00</t>
+    <t>2023-04-04T09:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T09:25:44+00:00</t>
+    <t>2023-04-04T10:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:05:29+00:00</t>
+    <t>2023-04-04T10:21:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:21:49+00:00</t>
+    <t>2023-04-04T10:30:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:30:43+00:00</t>
+    <t>2023-04-04T10:41:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:41:10+00:00</t>
+    <t>2023-04-04T10:41:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:41:37+00:00</t>
+    <t>2023-04-04T10:49:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T10:49:31+00:00</t>
+    <t>2023-04-04T13:12:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:12:12+00:00</t>
+    <t>2023-04-04T13:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-04T13:39:29+00:00</t>
+    <t>2023-04-17T11:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:49:04+00:00</t>
+    <t>2023-04-17T12:05:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:05:39+00:00</t>
+    <t>2023-04-17T12:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2700" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2702" uniqueCount="589">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:49:16+00:00</t>
+    <t>2023-05-26T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -1989,7 +1989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -2076,77 +2076,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>36</v>
       </c>
     </row>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:19+00:00</t>
+    <t>2023-05-26T12:35:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:35:50+00:00</t>
+    <t>2023-05-26T12:45:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:45:45+00:00</t>
+    <t>2023-05-26T12:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T12:47:23+00:00</t>
+    <t>2023-05-26T13:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:04:11+00:00</t>
+    <t>2023-05-26T13:05:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:05:32+00:00</t>
+    <t>2023-05-26T13:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T13:09:55+00:00</t>
+    <t>2023-05-26T14:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1629,7 +1629,7 @@
     <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.   Use `CodeableConcept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](servicerequest-example-di.html).</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/training-solution-1/ValueSet/vs-reason-for-assessment-or-test-not-performed</t>
+    <t>http://openhie.org/fhir/training-solution-1/ValueSet/vs-reason-for-assessment</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -2193,7 +2193,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="126.34765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="92.58203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.89453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:47:38+00:00</t>
+    <t>2023-05-26T14:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:52:17+00:00</t>
+    <t>2023-05-26T14:59:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T14:59:52+00:00</t>
+    <t>2023-05-26T15:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:03:26+00:00</t>
+    <t>2023-05-26T15:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2702" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2702" uniqueCount="588">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T15:10:57+00:00</t>
+    <t>2023-05-29T05:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -487,14 +487,14 @@
     <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 v2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 v2).  For further discussion and examples see the resource notes section below.</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:system}
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
-    <t>Slice based on the type of identifier</t>
-  </si>
-  <si>
-    <t>openAtEnd</t>
+    <t>Slice based on the type of identifier.</t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>Request.identifier</t>
@@ -554,9 +554,6 @@
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -3821,10 +3818,10 @@
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3856,10 +3853,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3885,16 +3882,16 @@
         <v>109</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="N15" t="s" s="2">
+      <c r="O15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>81</v>
@@ -3919,31 +3916,31 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3964,7 +3961,7 @@
         <v>132</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3975,10 +3972,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4001,19 +3998,19 @@
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>189</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>81</v>
@@ -4038,31 +4035,31 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Y16" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -4080,10 +4077,10 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -4094,10 +4091,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4209,10 +4206,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4291,10 +4288,10 @@
         <v>81</v>
       </c>
       <c r="AE18" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AF18" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AF18" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4326,10 +4323,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4352,19 +4349,19 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4413,7 +4410,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4431,10 +4428,10 @@
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -4445,10 +4442,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4560,10 +4557,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4642,10 +4639,10 @@
         <v>81</v>
       </c>
       <c r="AE21" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4677,10 +4674,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4706,16 +4703,16 @@
         <v>103</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4725,46 +4722,46 @@
         <v>81</v>
       </c>
       <c r="S22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4782,10 +4779,10 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4796,10 +4793,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B23" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4825,13 +4822,13 @@
         <v>163</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4881,7 +4878,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4899,10 +4896,10 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4913,10 +4910,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4942,14 +4939,14 @@
         <v>109</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4998,7 +4995,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5016,10 +5013,10 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -5030,10 +5027,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5059,14 +5056,14 @@
         <v>163</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5076,46 +5073,46 @@
         <v>81</v>
       </c>
       <c r="S25" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="T25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5133,10 +5130,10 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -5147,10 +5144,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5173,19 +5170,19 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5234,7 +5231,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5252,10 +5249,10 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>81</v>
@@ -5266,10 +5263,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5295,16 +5292,16 @@
         <v>163</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5314,46 +5311,46 @@
         <v>81</v>
       </c>
       <c r="S27" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5371,10 +5368,10 @@
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -5385,10 +5382,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5414,65 +5411,65 @@
         <v>103</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="N28" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T28" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="S28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T28" t="s" s="2">
+      <c r="U28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5490,10 +5487,10 @@
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -5504,10 +5501,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5533,13 +5530,13 @@
         <v>163</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5553,43 +5550,43 @@
         <v>81</v>
       </c>
       <c r="T29" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5607,10 +5604,10 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -5621,10 +5618,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5647,13 +5644,13 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5704,7 +5701,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5722,10 +5719,10 @@
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5736,10 +5733,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5762,16 +5759,16 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5821,7 +5818,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5839,10 +5836,10 @@
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5853,10 +5850,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5879,16 +5876,16 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5938,7 +5935,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5953,13 +5950,13 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
@@ -5970,10 +5967,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5999,13 +5996,13 @@
         <v>103</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6055,7 +6052,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6070,13 +6067,13 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -6087,14 +6084,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6113,13 +6110,13 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6170,7 +6167,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6185,13 +6182,13 @@
         <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -6202,14 +6199,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6228,13 +6225,13 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6285,7 +6282,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6300,13 +6297,13 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -6317,14 +6314,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6346,16 +6343,16 @@
         <v>147</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6404,7 +6401,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6419,13 +6416,13 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>345</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -6436,10 +6433,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6465,13 +6462,13 @@
         <v>109</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6497,14 +6494,14 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>351</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
       </c>
@@ -6521,7 +6518,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>89</v>
@@ -6536,27 +6533,27 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>356</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6582,13 +6579,13 @@
         <v>109</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6599,29 +6596,29 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y38" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="T38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y38" t="s" s="2">
+      <c r="Z38" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>363</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
       </c>
@@ -6638,7 +6635,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>89</v>
@@ -6653,16 +6650,16 @@
         <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>132</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6670,10 +6667,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6696,19 +6693,19 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6733,14 +6730,14 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Y39" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Y39" t="s" s="2">
+      <c r="Z39" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>374</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
       </c>
@@ -6757,7 +6754,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6775,13 +6772,13 @@
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>376</v>
-      </c>
       <c r="AN39" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -6789,10 +6786,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6818,10 +6815,10 @@
         <v>109</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6829,35 +6826,35 @@
         <v>81</v>
       </c>
       <c r="Q40" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="R40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y40" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="R40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y40" t="s" s="2">
+      <c r="Z40" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>382</v>
-      </c>
       <c r="AA40" t="s" s="2">
         <v>81</v>
       </c>
@@ -6874,7 +6871,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6889,16 +6886,16 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
@@ -6906,10 +6903,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6932,26 +6929,26 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="O41" t="s" s="2">
+      <c r="P41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q41" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="P41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q41" t="s" s="2">
-        <v>392</v>
-      </c>
       <c r="R41" t="s" s="2">
         <v>81</v>
       </c>
@@ -6995,7 +6992,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7010,13 +7007,13 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>81</v>
@@ -7027,14 +7024,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7053,16 +7050,16 @@
         <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7088,11 +7085,11 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -7110,7 +7107,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7125,27 +7122,27 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>405</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7257,10 +7254,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7339,10 +7336,10 @@
         <v>81</v>
       </c>
       <c r="AE44" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7374,10 +7371,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7400,19 +7397,19 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -7461,7 +7458,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -7479,10 +7476,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -7493,10 +7490,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7522,16 +7519,16 @@
         <v>163</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -7541,7 +7538,7 @@
         <v>81</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>81</v>
@@ -7580,7 +7577,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7598,10 +7595,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -7612,14 +7609,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7638,16 +7635,16 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7673,14 +7670,14 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>417</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
       </c>
@@ -7697,7 +7694,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7706,7 +7703,7 @@
         <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>101</v>
@@ -7715,24 +7712,24 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7755,17 +7752,17 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7814,7 +7811,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7832,10 +7829,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7846,10 +7843,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7872,13 +7869,13 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7929,7 +7926,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -7944,31 +7941,31 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL49" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AL49" t="s" s="2">
+      <c r="AM49" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>434</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7987,13 +7984,13 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8044,7 +8041,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8059,31 +8056,31 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AL50" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AM50" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>444</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8102,13 +8099,13 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8147,17 +8144,17 @@
         <v>81</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8172,33 +8169,33 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM51" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>456</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C52" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="B52" t="s" s="2">
+      <c r="D52" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="D52" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8217,13 +8214,13 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8274,7 +8271,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8289,27 +8286,27 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>456</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8332,13 +8329,13 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8365,14 +8362,14 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>464</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
       </c>
@@ -8389,7 +8386,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8410,25 +8407,25 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO53" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>466</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8447,13 +8444,13 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8504,7 +8501,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8519,31 +8516,31 @@
         <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AL54" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AM54" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>475</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8562,16 +8559,16 @@
         <v>90</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8621,7 +8618,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8636,31 +8633,31 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AL55" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AM55" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>486</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8679,16 +8676,16 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8714,14 +8711,14 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="Z56" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="Z56" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
       </c>
@@ -8738,7 +8735,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8753,16 +8750,16 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AL56" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="AL56" t="s" s="2">
+      <c r="AM56" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>497</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8770,14 +8767,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8796,16 +8793,16 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8855,7 +8852,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8870,16 +8867,16 @@
         <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AM57" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="AN57" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8887,10 +8884,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8913,13 +8910,13 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8946,14 +8943,14 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
       </c>
@@ -8970,7 +8967,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8991,10 +8988,10 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -9002,10 +8999,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9028,13 +9025,13 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9085,7 +9082,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9106,10 +9103,10 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9117,10 +9114,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9143,16 +9140,16 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9178,11 +9175,11 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9200,7 +9197,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9215,16 +9212,16 @@
         <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AL60" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
@@ -9232,10 +9229,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9347,10 +9344,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9429,10 +9426,10 @@
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9464,10 +9461,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9490,19 +9487,19 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="L63" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L63" t="s" s="2">
+      <c r="M63" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="N63" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>81</v>
@@ -9551,7 +9548,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9569,10 +9566,10 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>81</v>
@@ -9583,10 +9580,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9612,16 +9609,16 @@
         <v>163</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>81</v>
@@ -9631,7 +9628,7 @@
         <v>81</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>81</v>
@@ -9670,7 +9667,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9688,10 +9685,10 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>81</v>
@@ -9702,10 +9699,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9728,16 +9725,16 @@
         <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>532</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="N65" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9787,7 +9784,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9802,16 +9799,16 @@
         <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AL65" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AL65" t="s" s="2">
+      <c r="AM65" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="AM65" t="s" s="2">
-        <v>538</v>
-      </c>
       <c r="AN65" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>81</v>
@@ -9819,10 +9816,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9845,13 +9842,13 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9902,7 +9899,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9917,13 +9914,13 @@
         <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AL66" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="AL66" t="s" s="2">
+      <c r="AM66" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>81</v>
@@ -9934,14 +9931,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9960,16 +9957,16 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10019,7 +10016,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10034,13 +10031,13 @@
         <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AL67" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="AL67" t="s" s="2">
+      <c r="AM67" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>81</v>
@@ -10051,10 +10048,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10077,16 +10074,16 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>559</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10136,7 +10133,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10154,10 +10151,10 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>81</v>
@@ -10168,14 +10165,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10194,19 +10191,19 @@
         <v>90</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>566</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>567</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -10231,14 +10228,14 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>569</v>
-      </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
       </c>
@@ -10255,7 +10252,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10273,24 +10270,24 @@
         <v>81</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>571</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10313,13 +10310,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>50</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10370,7 +10367,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10385,27 +10382,27 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>577</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10431,10 +10428,10 @@
         <v>163</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>579</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>580</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10485,7 +10482,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10503,10 +10500,10 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>81</v>
@@ -10517,10 +10514,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10543,16 +10540,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10602,7 +10599,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10617,13 +10614,13 @@
         <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>132</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>81</v>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-29T05:00:29+00:00</t>
+    <t>2023-05-29T05:09:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-12T13:14:32+00:00</t>
+    <t>2023-06-13T16:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:44:52+00:00</t>
+    <t>2023-06-13T16:48:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:48:27+00:00</t>
+    <t>2023-06-13T16:56:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-13T16:56:41+00:00</t>
+    <t>2023-06-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-20T13:48:39+00:00</t>
+    <t>2023-06-20T13:48:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-HIV-lab-order.xlsx
+++ b/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-06-20T13:48:52+00:00</t>
+    <t>2023-06-20T13:53:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
